--- a/Outcome/Appendix/figure_data/fig1.xlsx
+++ b/Outcome/Appendix/figure_data/fig1.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="458">
   <si>
     <t xml:space="preserve">Group</t>
   </si>
@@ -90,10 +90,10 @@
     <t xml:space="preserve">Gonorrhoea</t>
   </si>
   <si>
-    <t xml:space="preserve">Syphilis</t>
+    <t xml:space="preserve">HBV</t>
   </si>
   <si>
-    <t xml:space="preserve">HBV</t>
+    <t xml:space="preserve">Syphilis</t>
   </si>
   <si>
     <t xml:space="preserve">CA</t>
@@ -126,10 +126,10 @@
     <t xml:space="preserve">Rubella</t>
   </si>
   <si>
-    <t xml:space="preserve">Pertussis</t>
+    <t xml:space="preserve">Other tetanus</t>
   </si>
   <si>
-    <t xml:space="preserve">Other tetanus</t>
+    <t xml:space="preserve">Pertussis</t>
   </si>
   <si>
     <t xml:space="preserve">Gastrointestinal ID</t>
@@ -171,1264 +171,1228 @@
     <t xml:space="preserve">Deaths_trend</t>
   </si>
   <si>
-    <t xml:space="preserve">31845.0306317441</t>
+    <t xml:space="preserve">32007.938205025</t>
   </si>
   <si>
-    <t xml:space="preserve">131.378872566199</t>
+    <t xml:space="preserve">131.595279394625</t>
   </si>
   <si>
-    <t xml:space="preserve">31983.3919787436</t>
+    <t xml:space="preserve">32136.7338977162</t>
   </si>
   <si>
-    <t xml:space="preserve">129.356808601631</t>
+    <t xml:space="preserve">129.585465488249</t>
   </si>
   <si>
-    <t xml:space="preserve">32121.753325743</t>
+    <t xml:space="preserve">32265.5295904075</t>
   </si>
   <si>
-    <t xml:space="preserve">127.334744637063</t>
+    <t xml:space="preserve">127.575651581873</t>
   </si>
   <si>
-    <t xml:space="preserve">32260.1146727425</t>
+    <t xml:space="preserve">32394.3252830988</t>
   </si>
   <si>
-    <t xml:space="preserve">125.312680672495</t>
+    <t xml:space="preserve">125.565837675497</t>
   </si>
   <si>
-    <t xml:space="preserve">32444.6818940592</t>
+    <t xml:space="preserve">32569.8989595389</t>
   </si>
   <si>
-    <t xml:space="preserve">123.429120533823</t>
+    <t xml:space="preserve">123.697633153906</t>
   </si>
   <si>
-    <t xml:space="preserve">32629.2491153759</t>
+    <t xml:space="preserve">32745.4726359791</t>
   </si>
   <si>
-    <t xml:space="preserve">121.545560395151</t>
+    <t xml:space="preserve">121.829428632316</t>
   </si>
   <si>
-    <t xml:space="preserve">32813.8163366925</t>
+    <t xml:space="preserve">32921.0463124193</t>
   </si>
   <si>
-    <t xml:space="preserve">119.662000256478</t>
+    <t xml:space="preserve">119.961224110725</t>
   </si>
   <si>
-    <t xml:space="preserve">32973.3177433544</t>
+    <t xml:space="preserve">33072.1883354914</t>
   </si>
   <si>
-    <t xml:space="preserve">117.842844550332</t>
+    <t xml:space="preserve">118.156093210655</t>
   </si>
   <si>
-    <t xml:space="preserve">33132.8191500163</t>
+    <t xml:space="preserve">33223.3303585635</t>
   </si>
   <si>
-    <t xml:space="preserve">116.023688844186</t>
+    <t xml:space="preserve">116.350962310586</t>
   </si>
   <si>
-    <t xml:space="preserve">33292.3205566782</t>
+    <t xml:space="preserve">33374.4723816356</t>
   </si>
   <si>
-    <t xml:space="preserve">114.20453313804</t>
+    <t xml:space="preserve">114.545831410516</t>
   </si>
   <si>
-    <t xml:space="preserve">33350.6836007549</t>
+    <t xml:space="preserve">33425.5603103997</t>
   </si>
   <si>
-    <t xml:space="preserve">112.662748120888</t>
+    <t xml:space="preserve">113.005013798115</t>
   </si>
   <si>
-    <t xml:space="preserve">33409.0466448315</t>
+    <t xml:space="preserve">33476.6482391638</t>
   </si>
   <si>
-    <t xml:space="preserve">111.120963103736</t>
+    <t xml:space="preserve">111.464196185715</t>
   </si>
   <si>
-    <t xml:space="preserve">33467.4096889081</t>
+    <t xml:space="preserve">33527.736167928</t>
   </si>
   <si>
-    <t xml:space="preserve">109.579178086584</t>
+    <t xml:space="preserve">109.923378573314</t>
   </si>
   <si>
-    <t xml:space="preserve">33658.0190935172</t>
+    <t xml:space="preserve">33712.9252713421</t>
   </si>
   <si>
-    <t xml:space="preserve">108.781609038557</t>
+    <t xml:space="preserve">109.137237158967</t>
   </si>
   <si>
-    <t xml:space="preserve">33848.6284981262</t>
+    <t xml:space="preserve">33898.1143747563</t>
   </si>
   <si>
-    <t xml:space="preserve">107.984039990529</t>
+    <t xml:space="preserve">108.351095744619</t>
   </si>
   <si>
-    <t xml:space="preserve">34039.2379027353</t>
+    <t xml:space="preserve">34083.3034781705</t>
   </si>
   <si>
-    <t xml:space="preserve">107.186470942502</t>
+    <t xml:space="preserve">107.564954330271</t>
   </si>
   <si>
-    <t xml:space="preserve">34663.409871345</t>
+    <t xml:space="preserve">34706.3874588333</t>
   </si>
   <si>
-    <t xml:space="preserve">106.780115638163</t>
+    <t xml:space="preserve">107.180992532578</t>
   </si>
   <si>
-    <t xml:space="preserve">35287.5818399547</t>
+    <t xml:space="preserve">35329.4714394962</t>
   </si>
   <si>
-    <t xml:space="preserve">106.373760333823</t>
+    <t xml:space="preserve">106.797030734884</t>
   </si>
   <si>
-    <t xml:space="preserve">35911.7538085645</t>
+    <t xml:space="preserve">35952.5554201591</t>
   </si>
   <si>
-    <t xml:space="preserve">105.967405029484</t>
+    <t xml:space="preserve">106.41306893719</t>
   </si>
   <si>
-    <t xml:space="preserve">36741.6510561177</t>
+    <t xml:space="preserve">36782.7257649649</t>
   </si>
   <si>
-    <t xml:space="preserve">106.246710454793</t>
+    <t xml:space="preserve">106.721639927116</t>
   </si>
   <si>
-    <t xml:space="preserve">37571.548303671</t>
+    <t xml:space="preserve">37612.8961097707</t>
   </si>
   <si>
-    <t xml:space="preserve">106.526015880101</t>
+    <t xml:space="preserve">107.030210917041</t>
   </si>
   <si>
-    <t xml:space="preserve">38401.4455512242</t>
+    <t xml:space="preserve">38443.0664545765</t>
   </si>
   <si>
-    <t xml:space="preserve">106.80532130541</t>
+    <t xml:space="preserve">107.338781906967</t>
   </si>
   <si>
-    <t xml:space="preserve">39399.2221848369</t>
+    <t xml:space="preserve">39435.6707482432</t>
   </si>
   <si>
-    <t xml:space="preserve">107.802225719568</t>
+    <t xml:space="preserve">108.329789555308</t>
   </si>
   <si>
-    <t xml:space="preserve">40396.9988184495</t>
+    <t xml:space="preserve">40428.2750419098</t>
   </si>
   <si>
-    <t xml:space="preserve">108.799130133726</t>
+    <t xml:space="preserve">109.320797203649</t>
   </si>
   <si>
-    <t xml:space="preserve">41394.7754520622</t>
+    <t xml:space="preserve">41420.8793355765</t>
   </si>
   <si>
-    <t xml:space="preserve">109.796034547884</t>
+    <t xml:space="preserve">110.311804851991</t>
   </si>
   <si>
-    <t xml:space="preserve">42274.8363131707</t>
+    <t xml:space="preserve">42299.3867492205</t>
   </si>
   <si>
-    <t xml:space="preserve">111.156307859227</t>
+    <t xml:space="preserve">111.630962669998</t>
   </si>
   <si>
-    <t xml:space="preserve">43154.8971742792</t>
+    <t xml:space="preserve">43177.8941628644</t>
   </si>
   <si>
-    <t xml:space="preserve">112.51658117057</t>
+    <t xml:space="preserve">112.950120488005</t>
   </si>
   <si>
-    <t xml:space="preserve">44034.9580353878</t>
+    <t xml:space="preserve">44056.4015765084</t>
   </si>
   <si>
-    <t xml:space="preserve">113.876854481913</t>
+    <t xml:space="preserve">114.269278306012</t>
   </si>
   <si>
-    <t xml:space="preserve">44632.9686193627</t>
+    <t xml:space="preserve">44657.6214668845</t>
   </si>
   <si>
-    <t xml:space="preserve">115.539540339689</t>
+    <t xml:space="preserve">115.917245160149</t>
   </si>
   <si>
-    <t xml:space="preserve">45230.9792033377</t>
+    <t xml:space="preserve">45258.8413572607</t>
   </si>
   <si>
-    <t xml:space="preserve">117.202226197464</t>
+    <t xml:space="preserve">117.565212014287</t>
   </si>
   <si>
-    <t xml:space="preserve">45828.9897873126</t>
+    <t xml:space="preserve">45860.0612476369</t>
   </si>
   <si>
-    <t xml:space="preserve">118.86491205524</t>
+    <t xml:space="preserve">119.213178868424</t>
   </si>
   <si>
-    <t xml:space="preserve">45862.284803995</t>
+    <t xml:space="preserve">45891.4315629576</t>
   </si>
   <si>
-    <t xml:space="preserve">120.773567102498</t>
+    <t xml:space="preserve">121.095274747255</t>
   </si>
   <si>
-    <t xml:space="preserve">45895.5798206774</t>
+    <t xml:space="preserve">45922.8018782784</t>
   </si>
   <si>
-    <t xml:space="preserve">122.682222149757</t>
+    <t xml:space="preserve">122.977370626085</t>
   </si>
   <si>
-    <t xml:space="preserve">45928.8748373598</t>
+    <t xml:space="preserve">45954.1721935991</t>
   </si>
   <si>
-    <t xml:space="preserve">124.590877197015</t>
+    <t xml:space="preserve">124.859466504916</t>
   </si>
   <si>
-    <t xml:space="preserve">45443.8183796122</t>
+    <t xml:space="preserve">45464.0218822133</t>
   </si>
   <si>
-    <t xml:space="preserve">126.033736494543</t>
+    <t xml:space="preserve">126.257436909944</t>
   </si>
   <si>
-    <t xml:space="preserve">44958.7619218645</t>
+    <t xml:space="preserve">44973.8715708275</t>
   </si>
   <si>
-    <t xml:space="preserve">127.476595792071</t>
+    <t xml:space="preserve">127.655407314973</t>
   </si>
   <si>
-    <t xml:space="preserve">44473.7054641168</t>
+    <t xml:space="preserve">44483.7212594416</t>
   </si>
   <si>
-    <t xml:space="preserve">128.919455089599</t>
+    <t xml:space="preserve">129.053377720001</t>
   </si>
   <si>
-    <t xml:space="preserve">43892.9541857723</t>
+    <t xml:space="preserve">43898.4065391347</t>
   </si>
   <si>
-    <t xml:space="preserve">129.633565286027</t>
+    <t xml:space="preserve">129.738006260393</t>
   </si>
   <si>
-    <t xml:space="preserve">43312.2029074277</t>
+    <t xml:space="preserve">43313.0918188277</t>
   </si>
   <si>
-    <t xml:space="preserve">130.347675482455</t>
+    <t xml:space="preserve">130.422634800785</t>
   </si>
   <si>
-    <t xml:space="preserve">42731.4516290831</t>
+    <t xml:space="preserve">42727.7770985208</t>
   </si>
   <si>
-    <t xml:space="preserve">131.061785678883</t>
+    <t xml:space="preserve">131.107263341178</t>
   </si>
   <si>
-    <t xml:space="preserve">42424.2969599265</t>
+    <t xml:space="preserve">42422.9353345597</t>
   </si>
   <si>
-    <t xml:space="preserve">131.274654034885</t>
+    <t xml:space="preserve">131.329730954299</t>
   </si>
   <si>
-    <t xml:space="preserve">42117.1422907698</t>
+    <t xml:space="preserve">42118.0935705986</t>
   </si>
   <si>
-    <t xml:space="preserve">131.487522390886</t>
+    <t xml:space="preserve">131.552198567421</t>
   </si>
   <si>
-    <t xml:space="preserve">41809.9876216132</t>
+    <t xml:space="preserve">41813.2518066376</t>
   </si>
   <si>
-    <t xml:space="preserve">131.700390746888</t>
+    <t xml:space="preserve">131.774666180543</t>
   </si>
   <si>
-    <t xml:space="preserve">41782.6208108228</t>
+    <t xml:space="preserve">41786.5777417676</t>
   </si>
   <si>
-    <t xml:space="preserve">131.619928992435</t>
+    <t xml:space="preserve">131.720907840177</t>
   </si>
   <si>
-    <t xml:space="preserve">41755.2540000323</t>
+    <t xml:space="preserve">41759.9036768977</t>
   </si>
   <si>
-    <t xml:space="preserve">131.539467237981</t>
+    <t xml:space="preserve">131.667149499811</t>
   </si>
   <si>
-    <t xml:space="preserve">41727.8871892419</t>
+    <t xml:space="preserve">41733.2296120278</t>
   </si>
   <si>
-    <t xml:space="preserve">131.459005483528</t>
+    <t xml:space="preserve">131.613391159444</t>
   </si>
   <si>
-    <t xml:space="preserve">41714.2079611083</t>
+    <t xml:space="preserve">41719.2242180998</t>
   </si>
   <si>
-    <t xml:space="preserve">130.842806069358</t>
+    <t xml:space="preserve">131.000567540192</t>
   </si>
   <si>
-    <t xml:space="preserve">41700.5287329747</t>
+    <t xml:space="preserve">41705.2188241717</t>
   </si>
   <si>
-    <t xml:space="preserve">130.226606655188</t>
+    <t xml:space="preserve">130.387743920941</t>
   </si>
   <si>
-    <t xml:space="preserve">41686.8495048411</t>
+    <t xml:space="preserve">41691.2134302437</t>
   </si>
   <si>
-    <t xml:space="preserve">129.610407241019</t>
+    <t xml:space="preserve">129.774920301689</t>
   </si>
   <si>
-    <t xml:space="preserve">41599.9055586865</t>
+    <t xml:space="preserve">41607.0609355192</t>
   </si>
   <si>
-    <t xml:space="preserve">128.536928442663</t>
+    <t xml:space="preserve">128.715950052794</t>
   </si>
   <si>
-    <t xml:space="preserve">41512.9616125318</t>
+    <t xml:space="preserve">41522.9084407947</t>
   </si>
   <si>
-    <t xml:space="preserve">127.463449644308</t>
+    <t xml:space="preserve">127.656979803899</t>
   </si>
   <si>
-    <t xml:space="preserve">41426.0176663772</t>
+    <t xml:space="preserve">41438.7559460702</t>
   </si>
   <si>
-    <t xml:space="preserve">126.389970845952</t>
+    <t xml:space="preserve">126.598009555004</t>
   </si>
   <si>
-    <t xml:space="preserve">41282.1070146991</t>
+    <t xml:space="preserve">41297.5434630961</t>
   </si>
   <si>
-    <t xml:space="preserve">125.795759783088</t>
+    <t xml:space="preserve">126.033036912573</t>
   </si>
   <si>
-    <t xml:space="preserve">41138.1963630209</t>
+    <t xml:space="preserve">41156.330980122</t>
   </si>
   <si>
-    <t xml:space="preserve">125.201548720224</t>
+    <t xml:space="preserve">125.468064270143</t>
   </si>
   <si>
-    <t xml:space="preserve">40994.2857113427</t>
+    <t xml:space="preserve">41015.1184971478</t>
   </si>
   <si>
-    <t xml:space="preserve">124.60733765736</t>
+    <t xml:space="preserve">124.903091627712</t>
   </si>
   <si>
-    <t xml:space="preserve">40954.5845522779</t>
+    <t xml:space="preserve">40971.5742843115</t>
   </si>
   <si>
-    <t xml:space="preserve">124.970005783862</t>
+    <t xml:space="preserve">125.26056751622</t>
   </si>
   <si>
-    <t xml:space="preserve">40914.8833932131</t>
+    <t xml:space="preserve">40928.0300714752</t>
   </si>
   <si>
-    <t xml:space="preserve">125.332673910365</t>
+    <t xml:space="preserve">125.618043404727</t>
   </si>
   <si>
-    <t xml:space="preserve">40875.1822341484</t>
+    <t xml:space="preserve">40884.4858586389</t>
   </si>
   <si>
-    <t xml:space="preserve">125.695342036868</t>
+    <t xml:space="preserve">125.975519293234</t>
   </si>
   <si>
-    <t xml:space="preserve">40895.3139122165</t>
+    <t xml:space="preserve">40900.2009340788</t>
   </si>
   <si>
-    <t xml:space="preserve">125.82647439994</t>
+    <t xml:space="preserve">126.076161748974</t>
   </si>
   <si>
-    <t xml:space="preserve">40915.4455902846</t>
+    <t xml:space="preserve">40915.9160095187</t>
   </si>
   <si>
-    <t xml:space="preserve">125.957606763012</t>
+    <t xml:space="preserve">126.176804204714</t>
   </si>
   <si>
-    <t xml:space="preserve">40935.5772683527</t>
+    <t xml:space="preserve">40931.6310849586</t>
   </si>
   <si>
-    <t xml:space="preserve">126.088739126085</t>
+    <t xml:space="preserve">126.277446660454</t>
   </si>
   <si>
-    <t xml:space="preserve">41057.8577632684</t>
+    <t xml:space="preserve">41052.1391241657</t>
   </si>
   <si>
-    <t xml:space="preserve">126.188989542798</t>
+    <t xml:space="preserve">126.380124911419</t>
   </si>
   <si>
-    <t xml:space="preserve">41180.1382581841</t>
+    <t xml:space="preserve">41172.6471633728</t>
   </si>
   <si>
-    <t xml:space="preserve">126.289239959511</t>
+    <t xml:space="preserve">126.482803162383</t>
   </si>
   <si>
-    <t xml:space="preserve">41302.4187530998</t>
+    <t xml:space="preserve">41293.1552025799</t>
   </si>
   <si>
-    <t xml:space="preserve">126.389490376224</t>
+    <t xml:space="preserve">126.585481413348</t>
   </si>
   <si>
-    <t xml:space="preserve">41480.8337970559</t>
+    <t xml:space="preserve">41473.6213899317</t>
   </si>
   <si>
-    <t xml:space="preserve">126.494018887207</t>
+    <t xml:space="preserve">126.697292740283</t>
   </si>
   <si>
-    <t xml:space="preserve">41659.2488410121</t>
+    <t xml:space="preserve">41654.0875772835</t>
   </si>
   <si>
-    <t xml:space="preserve">126.59854739819</t>
+    <t xml:space="preserve">126.809104067218</t>
   </si>
   <si>
-    <t xml:space="preserve">41837.6638849682</t>
+    <t xml:space="preserve">41834.5537646354</t>
   </si>
   <si>
-    <t xml:space="preserve">126.703075909174</t>
+    <t xml:space="preserve">126.920915394153</t>
   </si>
   <si>
-    <t xml:space="preserve">42150.0461041207</t>
+    <t xml:space="preserve">42144.9586284467</t>
   </si>
   <si>
-    <t xml:space="preserve">125.94532088582</t>
+    <t xml:space="preserve">126.159063145931</t>
   </si>
   <si>
-    <t xml:space="preserve">42462.4283232732</t>
+    <t xml:space="preserve">42455.363492258</t>
   </si>
   <si>
-    <t xml:space="preserve">125.187565862467</t>
+    <t xml:space="preserve">125.397210897708</t>
   </si>
   <si>
-    <t xml:space="preserve">42774.8105424258</t>
+    <t xml:space="preserve">42765.7683560693</t>
   </si>
   <si>
-    <t xml:space="preserve">124.429810839113</t>
+    <t xml:space="preserve">124.635358649486</t>
   </si>
   <si>
-    <t xml:space="preserve">42914.3068820209</t>
+    <t xml:space="preserve">42902.7245480427</t>
   </si>
   <si>
-    <t xml:space="preserve">122.788357644638</t>
+    <t xml:space="preserve">122.996051343773</t>
   </si>
   <si>
-    <t xml:space="preserve">43053.803221616</t>
+    <t xml:space="preserve">43039.6807400161</t>
   </si>
   <si>
-    <t xml:space="preserve">121.146904450162</t>
+    <t xml:space="preserve">121.35674403806</t>
   </si>
   <si>
-    <t xml:space="preserve">43193.2995612111</t>
+    <t xml:space="preserve">43176.6369319894</t>
   </si>
   <si>
-    <t xml:space="preserve">119.505451255687</t>
+    <t xml:space="preserve">119.717436732347</t>
   </si>
   <si>
-    <t xml:space="preserve">42974.3158149335</t>
+    <t xml:space="preserve">42955.8811421153</t>
   </si>
   <si>
-    <t xml:space="preserve">118.027884701114</t>
+    <t xml:space="preserve">118.227965970821</t>
   </si>
   <si>
-    <t xml:space="preserve">42755.3320686558</t>
+    <t xml:space="preserve">42735.1253522412</t>
   </si>
   <si>
-    <t xml:space="preserve">116.55031814654</t>
+    <t xml:space="preserve">116.738495209295</t>
   </si>
   <si>
-    <t xml:space="preserve">42536.3483223781</t>
+    <t xml:space="preserve">42514.3695623672</t>
   </si>
   <si>
-    <t xml:space="preserve">115.072751591967</t>
+    <t xml:space="preserve">115.249024447769</t>
   </si>
   <si>
-    <t xml:space="preserve">42499.2480372294</t>
+    <t xml:space="preserve">42470.8119706494</t>
   </si>
   <si>
-    <t xml:space="preserve">113.704067952559</t>
+    <t xml:space="preserve">113.814211167113</t>
   </si>
   <si>
-    <t xml:space="preserve">42462.1477520806</t>
+    <t xml:space="preserve">42427.2543789316</t>
   </si>
   <si>
-    <t xml:space="preserve">112.33538431315</t>
+    <t xml:space="preserve">112.379397886458</t>
   </si>
   <si>
-    <t xml:space="preserve">42425.0474669319</t>
+    <t xml:space="preserve">42383.6967872138</t>
   </si>
   <si>
-    <t xml:space="preserve">110.966700673742</t>
+    <t xml:space="preserve">110.944584605802</t>
   </si>
   <si>
-    <t xml:space="preserve">42615.5143751578</t>
+    <t xml:space="preserve">42566.1266116326</t>
   </si>
   <si>
-    <t xml:space="preserve">109.458587409544</t>
+    <t xml:space="preserve">109.358307641983</t>
   </si>
   <si>
-    <t xml:space="preserve">42805.9812833837</t>
+    <t xml:space="preserve">42748.5564360515</t>
   </si>
   <si>
-    <t xml:space="preserve">107.950474145346</t>
+    <t xml:space="preserve">107.772030678165</t>
   </si>
   <si>
-    <t xml:space="preserve">42996.4481916095</t>
+    <t xml:space="preserve">42930.9862604703</t>
   </si>
   <si>
-    <t xml:space="preserve">106.442360881147</t>
+    <t xml:space="preserve">106.185753714347</t>
   </si>
   <si>
-    <t xml:space="preserve">42872.8053624368</t>
+    <t xml:space="preserve">42803.3287023829</t>
   </si>
   <si>
-    <t xml:space="preserve">104.10150633525</t>
+    <t xml:space="preserve">103.797097017632</t>
   </si>
   <si>
-    <t xml:space="preserve">42749.162533264</t>
+    <t xml:space="preserve">42675.6711442956</t>
   </si>
   <si>
-    <t xml:space="preserve">101.760651789354</t>
+    <t xml:space="preserve">101.408440320918</t>
   </si>
   <si>
-    <t xml:space="preserve">42625.5197040913</t>
+    <t xml:space="preserve">42548.0135862083</t>
   </si>
   <si>
-    <t xml:space="preserve">99.4197972434568</t>
+    <t xml:space="preserve">99.0197836242033</t>
   </si>
   <si>
-    <t xml:space="preserve">42353.6003762964</t>
+    <t xml:space="preserve">42277.5017668097</t>
   </si>
   <si>
-    <t xml:space="preserve">96.9537692973244</t>
+    <t xml:space="preserve">96.5263978526763</t>
   </si>
   <si>
-    <t xml:space="preserve">42081.6810485015</t>
+    <t xml:space="preserve">42006.9899474112</t>
   </si>
   <si>
-    <t xml:space="preserve">94.487741351192</t>
+    <t xml:space="preserve">94.0330120811494</t>
   </si>
   <si>
-    <t xml:space="preserve">41809.7617207066</t>
+    <t xml:space="preserve">41736.4781280126</t>
   </si>
   <si>
-    <t xml:space="preserve">92.0217134050596</t>
+    <t xml:space="preserve">91.5396263096225</t>
   </si>
   <si>
-    <t xml:space="preserve">41763.0788000201</t>
+    <t xml:space="preserve">41697.7854061482</t>
   </si>
   <si>
-    <t xml:space="preserve">89.5894870379548</t>
+    <t xml:space="preserve">89.1198922436701</t>
   </si>
   <si>
-    <t xml:space="preserve">41716.3958793336</t>
+    <t xml:space="preserve">41659.0926842838</t>
   </si>
   <si>
-    <t xml:space="preserve">87.1572606708501</t>
+    <t xml:space="preserve">86.7001581777176</t>
   </si>
   <si>
-    <t xml:space="preserve">41669.7129586471</t>
+    <t xml:space="preserve">41620.3999624194</t>
   </si>
   <si>
-    <t xml:space="preserve">84.7250343037453</t>
+    <t xml:space="preserve">84.2804241117652</t>
   </si>
   <si>
-    <t xml:space="preserve">41467.6436969136</t>
+    <t xml:space="preserve">41426.7242692411</t>
   </si>
   <si>
-    <t xml:space="preserve">81.7570402825488</t>
+    <t xml:space="preserve">81.3824485564937</t>
   </si>
   <si>
-    <t xml:space="preserve">41265.5744351801</t>
+    <t xml:space="preserve">41233.0485760628</t>
   </si>
   <si>
-    <t xml:space="preserve">78.7890462613523</t>
+    <t xml:space="preserve">78.4844730012222</t>
   </si>
   <si>
-    <t xml:space="preserve">41063.5051734466</t>
+    <t xml:space="preserve">41039.3728828844</t>
   </si>
   <si>
-    <t xml:space="preserve">75.8210522401558</t>
+    <t xml:space="preserve">75.5864974459507</t>
   </si>
   <si>
-    <t xml:space="preserve">40906.6277966669</t>
+    <t xml:space="preserve">40889.4544350987</t>
   </si>
   <si>
-    <t xml:space="preserve">72.2605430773848</t>
+    <t xml:space="preserve">72.095907586562</t>
   </si>
   <si>
-    <t xml:space="preserve">40749.7504198872</t>
+    <t xml:space="preserve">40739.5359873129</t>
   </si>
   <si>
-    <t xml:space="preserve">68.7000339146138</t>
+    <t xml:space="preserve">68.6053177271733</t>
   </si>
   <si>
-    <t xml:space="preserve">40592.8730431076</t>
+    <t xml:space="preserve">40589.6175395272</t>
   </si>
   <si>
-    <t xml:space="preserve">65.1395247518429</t>
+    <t xml:space="preserve">65.1147278677845</t>
   </si>
   <si>
-    <t xml:space="preserve">41145.1340587022</t>
+    <t xml:space="preserve">41143.4837765897</t>
   </si>
   <si>
-    <t xml:space="preserve">62.3804897024015</t>
+    <t xml:space="preserve">62.3738760003132</t>
   </si>
   <si>
-    <t xml:space="preserve">41697.3950742969</t>
+    <t xml:space="preserve">41697.3500136521</t>
   </si>
   <si>
-    <t xml:space="preserve">59.6214546529601</t>
+    <t xml:space="preserve">59.6330241328418</t>
   </si>
   <si>
-    <t xml:space="preserve">42249.6560898916</t>
+    <t xml:space="preserve">42251.2162507146</t>
   </si>
   <si>
-    <t xml:space="preserve">56.8624196035187</t>
+    <t xml:space="preserve">56.8921722653705</t>
   </si>
   <si>
-    <t xml:space="preserve">43066.562225286</t>
+    <t xml:space="preserve">43072.0592803167</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9506552161577</t>
+    <t xml:space="preserve">54.9917663950597</t>
   </si>
   <si>
-    <t xml:space="preserve">43883.4683606803</t>
+    <t xml:space="preserve">43892.9023099187</t>
   </si>
   <si>
-    <t xml:space="preserve">53.0388908287967</t>
+    <t xml:space="preserve">53.0913605247489</t>
   </si>
   <si>
-    <t xml:space="preserve">44700.3744960746</t>
+    <t xml:space="preserve">44713.7453395207</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1271264414357</t>
+    <t xml:space="preserve">51.1909546544381</t>
   </si>
   <si>
-    <t xml:space="preserve">45295.5007525747</t>
+    <t xml:space="preserve">45312.0145165621</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4356676740243</t>
+    <t xml:space="preserve">49.5227620767654</t>
   </si>
   <si>
-    <t xml:space="preserve">45890.6270090747</t>
+    <t xml:space="preserve">45910.2836936036</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7442089066129</t>
+    <t xml:space="preserve">47.8545694990927</t>
   </si>
   <si>
-    <t xml:space="preserve">46485.7532655747</t>
+    <t xml:space="preserve">46508.552870645</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0527501392016</t>
+    <t xml:space="preserve">46.18637692142</t>
   </si>
   <si>
-    <t xml:space="preserve">47270.6415389412</t>
+    <t xml:space="preserve">47293.1602567542</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9353785066444</t>
+    <t xml:space="preserve">45.064587766734</t>
   </si>
   <si>
-    <t xml:space="preserve">48055.5298123076</t>
+    <t xml:space="preserve">48077.7676428633</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8180068740872</t>
+    <t xml:space="preserve">43.942798612048</t>
   </si>
   <si>
-    <t xml:space="preserve">48840.4180856741</t>
+    <t xml:space="preserve">48862.3750289725</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7006352415301</t>
+    <t xml:space="preserve">42.821009457362</t>
   </si>
   <si>
-    <t xml:space="preserve">49631.7019839496</t>
+    <t xml:space="preserve">49648.5718217678</t>
   </si>
   <si>
-    <t xml:space="preserve">42.503180857275</t>
+    <t xml:space="preserve">42.6057759180881</t>
   </si>
   <si>
-    <t xml:space="preserve">50422.9858822252</t>
+    <t xml:space="preserve">50434.768614563</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3057264730199</t>
+    <t xml:space="preserve">42.3905423788142</t>
   </si>
   <si>
-    <t xml:space="preserve">51214.2697805008</t>
+    <t xml:space="preserve">51220.9654073582</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1082720887648</t>
+    <t xml:space="preserve">42.1753088395403</t>
   </si>
   <si>
-    <t xml:space="preserve">51296.5937408228</t>
+    <t xml:space="preserve">51299.1611431819</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3139895032949</t>
+    <t xml:space="preserve">42.3850251914737</t>
   </si>
   <si>
-    <t xml:space="preserve">51378.9177011449</t>
+    <t xml:space="preserve">51377.3568790056</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5197069178251</t>
+    <t xml:space="preserve">42.5947415434072</t>
   </si>
   <si>
-    <t xml:space="preserve">51461.2416614669</t>
+    <t xml:space="preserve">51455.5526148292</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7254243323553</t>
+    <t xml:space="preserve">42.8044578953406</t>
   </si>
   <si>
-    <t xml:space="preserve">51474.5197929494</t>
+    <t xml:space="preserve">51461.8928993406</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1705451984742</t>
+    <t xml:space="preserve">43.2666781283463</t>
   </si>
   <si>
-    <t xml:space="preserve">51487.7979244319</t>
+    <t xml:space="preserve">51468.2331838521</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6156660645932</t>
+    <t xml:space="preserve">43.728898361352</t>
   </si>
   <si>
-    <t xml:space="preserve">51501.0760559144</t>
+    <t xml:space="preserve">51474.5734683635</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0607869307122</t>
+    <t xml:space="preserve">44.1911185943577</t>
   </si>
   <si>
-    <t xml:space="preserve">51974.263335443</t>
+    <t xml:space="preserve">51934.6341776679</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4338109156703</t>
+    <t xml:space="preserve">45.548784101615</t>
   </si>
   <si>
-    <t xml:space="preserve">52447.4506149717</t>
+    <t xml:space="preserve">52394.6948869724</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8068349006285</t>
+    <t xml:space="preserve">46.9064496088723</t>
   </si>
   <si>
-    <t xml:space="preserve">52920.6378945003</t>
+    <t xml:space="preserve">52854.7555962769</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1798588855867</t>
+    <t xml:space="preserve">48.2641151161295</t>
   </si>
   <si>
-    <t xml:space="preserve">53324.8622249725</t>
+    <t xml:space="preserve">53253.9912908093</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3278127445376</t>
+    <t xml:space="preserve">49.3833764526204</t>
   </si>
   <si>
-    <t xml:space="preserve">53729.0865554446</t>
+    <t xml:space="preserve">53653.2269853416</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4757666034886</t>
+    <t xml:space="preserve">50.5026377891113</t>
   </si>
   <si>
-    <t xml:space="preserve">54133.3108859168</t>
+    <t xml:space="preserve">54052.462679874</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6237204624395</t>
+    <t xml:space="preserve">51.6218991256022</t>
   </si>
   <si>
-    <t xml:space="preserve">54192.164788267</t>
+    <t xml:space="preserve">54118.339897319</t>
   </si>
   <si>
-    <t xml:space="preserve">51.4258571278671</t>
+    <t xml:space="preserve">51.4317776086729</t>
   </si>
   <si>
-    <t xml:space="preserve">54251.0186906172</t>
+    <t xml:space="preserve">54184.2171147639</t>
   </si>
   <si>
-    <t xml:space="preserve">51.2279937932946</t>
+    <t xml:space="preserve">51.2416560917436</t>
   </si>
   <si>
-    <t xml:space="preserve">54309.8725929675</t>
+    <t xml:space="preserve">54250.0943322089</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0301304587222</t>
+    <t xml:space="preserve">51.0515345748143</t>
   </si>
   <si>
-    <t xml:space="preserve">54821.833557705</t>
+    <t xml:space="preserve">54765.5803050059</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6338423471267</t>
+    <t xml:space="preserve">50.6793241512309</t>
   </si>
   <si>
-    <t xml:space="preserve">55333.7945224426</t>
+    <t xml:space="preserve">55281.066277803</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2375542355312</t>
+    <t xml:space="preserve">50.3071137276475</t>
   </si>
   <si>
-    <t xml:space="preserve">55845.7554871802</t>
+    <t xml:space="preserve">55796.5522506</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8412661239356</t>
+    <t xml:space="preserve">49.9349033040641</t>
   </si>
   <si>
-    <t xml:space="preserve">56760.9260511073</t>
+    <t xml:space="preserve">56712.4753850695</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4876224699304</t>
+    <t xml:space="preserve">49.5586558951568</t>
   </si>
   <si>
-    <t xml:space="preserve">57676.0966150344</t>
+    <t xml:space="preserve">57628.398519539</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1339788159251</t>
+    <t xml:space="preserve">49.1824084862494</t>
   </si>
   <si>
-    <t xml:space="preserve">58591.2671789616</t>
+    <t xml:space="preserve">58544.3216540086</t>
   </si>
   <si>
-    <t xml:space="preserve">48.7803351619199</t>
+    <t xml:space="preserve">48.806161077342</t>
   </si>
   <si>
-    <t xml:space="preserve">59150.252892602</t>
+    <t xml:space="preserve">59103.9883565948</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8857735707513</t>
+    <t xml:space="preserve">47.8913577279242</t>
   </si>
   <si>
-    <t xml:space="preserve">59709.2386062424</t>
+    <t xml:space="preserve">59663.655059181</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9912119795828</t>
+    <t xml:space="preserve">46.9765543785063</t>
   </si>
   <si>
-    <t xml:space="preserve">60268.2243198829</t>
+    <t xml:space="preserve">60223.3217617672</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0966503884142</t>
+    <t xml:space="preserve">46.0617510290884</t>
   </si>
   <si>
-    <t xml:space="preserve">61234.0946515827</t>
+    <t xml:space="preserve">61175.8080453494</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6011979013828</t>
+    <t xml:space="preserve">45.573402140545</t>
   </si>
   <si>
-    <t xml:space="preserve">62199.9649832825</t>
+    <t xml:space="preserve">62128.2943289315</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1057454143513</t>
+    <t xml:space="preserve">45.0850532520016</t>
   </si>
   <si>
-    <t xml:space="preserve">63165.8353149823</t>
+    <t xml:space="preserve">63080.7806125137</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6102929273198</t>
+    <t xml:space="preserve">44.5967043634582</t>
   </si>
   <si>
-    <t xml:space="preserve">64343.5190406572</t>
+    <t xml:space="preserve">64239.1621116454</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2858585663493</t>
+    <t xml:space="preserve">44.2836596770621</t>
   </si>
   <si>
-    <t xml:space="preserve">65521.2027663321</t>
+    <t xml:space="preserve">65397.5436107771</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9614242053787</t>
+    <t xml:space="preserve">43.9706149906659</t>
   </si>
   <si>
-    <t xml:space="preserve">66698.886492007</t>
+    <t xml:space="preserve">66555.9251099088</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6369898444082</t>
+    <t xml:space="preserve">43.6575703042697</t>
   </si>
   <si>
-    <t xml:space="preserve">67758.8760462277</t>
+    <t xml:space="preserve">67605.018270543</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1587357391402</t>
+    <t xml:space="preserve">43.1659504432059</t>
   </si>
   <si>
-    <t xml:space="preserve">68818.8656004483</t>
+    <t xml:space="preserve">68654.1114311772</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6804816338721</t>
+    <t xml:space="preserve">42.6743305821421</t>
   </si>
   <si>
-    <t xml:space="preserve">69878.8551546689</t>
+    <t xml:space="preserve">69703.2045918114</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2022275286041</t>
+    <t xml:space="preserve">42.1827107210783</t>
   </si>
   <si>
-    <t xml:space="preserve">70538.0387258036</t>
+    <t xml:space="preserve">70357.4531616357</t>
   </si>
   <si>
-    <t xml:space="preserve">41.324298590148</t>
+    <t xml:space="preserve">41.293260691834</t>
   </si>
   <si>
-    <t xml:space="preserve">71197.2222969383</t>
+    <t xml:space="preserve">71011.7017314601</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4463696516918</t>
+    <t xml:space="preserve">40.4038106625897</t>
   </si>
   <si>
-    <t xml:space="preserve">71856.405868073</t>
+    <t xml:space="preserve">71665.9503012844</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5684407132357</t>
+    <t xml:space="preserve">39.5143606333454</t>
   </si>
   <si>
-    <t xml:space="preserve">71261.3609820052</t>
+    <t xml:space="preserve">71060.4180524365</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1462238150232</t>
+    <t xml:space="preserve">38.1118258884799</t>
   </si>
   <si>
-    <t xml:space="preserve">70666.3160959374</t>
+    <t xml:space="preserve">70454.8858035885</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7240069168107</t>
+    <t xml:space="preserve">36.7092911436145</t>
   </si>
   <si>
-    <t xml:space="preserve">70071.2712098697</t>
+    <t xml:space="preserve">69849.3535547406</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3017900185982</t>
+    <t xml:space="preserve">35.306756398749</t>
   </si>
   <si>
-    <t xml:space="preserve">67722.8247237004</t>
+    <t xml:space="preserve">67483.8781712794</t>
   </si>
   <si>
-    <t xml:space="preserve">33.828510329747</t>
+    <t xml:space="preserve">33.8631099664349</t>
   </si>
   <si>
-    <t xml:space="preserve">65374.3782375312</t>
+    <t xml:space="preserve">65118.4027878182</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3552306408959</t>
+    <t xml:space="preserve">32.4194635341207</t>
   </si>
   <si>
-    <t xml:space="preserve">63025.931751362</t>
+    <t xml:space="preserve">62752.927404357</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8819509520448</t>
+    <t xml:space="preserve">30.9758171018066</t>
   </si>
   <si>
-    <t xml:space="preserve">60027.37261845</t>
+    <t xml:space="preserve">59754.3606844021</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7657830575431</t>
+    <t xml:space="preserve">29.8553283904234</t>
   </si>
   <si>
-    <t xml:space="preserve">57028.813485538</t>
+    <t xml:space="preserve">56755.7939644472</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6496151630415</t>
+    <t xml:space="preserve">28.7348396790403</t>
   </si>
   <si>
-    <t xml:space="preserve">54030.254352626</t>
+    <t xml:space="preserve">53757.2272444923</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5334472685398</t>
+    <t xml:space="preserve">27.6143509676571</t>
   </si>
   <si>
-    <t xml:space="preserve">51292.4335805307</t>
+    <t xml:space="preserve">51012.2995969618</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6868970034745</t>
+    <t xml:space="preserve">26.7526015687842</t>
   </si>
   <si>
-    <t xml:space="preserve">48554.6128084354</t>
+    <t xml:space="preserve">48267.3719494313</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8403467384091</t>
+    <t xml:space="preserve">25.8908521699113</t>
   </si>
   <si>
-    <t xml:space="preserve">45816.7920363401</t>
+    <t xml:space="preserve">45522.4443019008</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9937964733438</t>
+    <t xml:space="preserve">25.0291027710384</t>
   </si>
   <si>
-    <t xml:space="preserve">42998.5588058532</t>
+    <t xml:space="preserve">42713.8391498619</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3578889850958</t>
+    <t xml:space="preserve">24.3962423320184</t>
   </si>
   <si>
-    <t xml:space="preserve">40180.3255753662</t>
+    <t xml:space="preserve">39905.2339978231</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7219814968478</t>
+    <t xml:space="preserve">23.7633818929984</t>
   </si>
   <si>
-    <t xml:space="preserve">37362.0923448792</t>
+    <t xml:space="preserve">37096.6288457842</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0860740085997</t>
+    <t xml:space="preserve">23.1305214539784</t>
   </si>
   <si>
-    <t xml:space="preserve">35482.5569771805</t>
+    <t xml:space="preserve">35263.1371878655</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1305952375601</t>
+    <t xml:space="preserve">23.1824163160089</t>
   </si>
   <si>
-    <t xml:space="preserve">33603.0216094819</t>
+    <t xml:space="preserve">33429.6455299469</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1751164665204</t>
+    <t xml:space="preserve">23.2343111780393</t>
   </si>
   <si>
-    <t xml:space="preserve">31723.4862417832</t>
+    <t xml:space="preserve">31596.1538720282</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2196376954808</t>
+    <t xml:space="preserve">23.2862060400697</t>
   </si>
   <si>
-    <t xml:space="preserve">30526.1930036546</t>
+    <t xml:space="preserve">30431.7596533355</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5962001329045</t>
+    <t xml:space="preserve">23.6460701150931</t>
   </si>
   <si>
-    <t xml:space="preserve">29328.8997655261</t>
+    <t xml:space="preserve">29267.3654346427</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9727625703282</t>
+    <t xml:space="preserve">24.0059341901164</t>
   </si>
   <si>
-    <t xml:space="preserve">28131.6065273975</t>
+    <t xml:space="preserve">28102.97121595</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3493250077519</t>
+    <t xml:space="preserve">24.3657982651398</t>
   </si>
   <si>
-    <t xml:space="preserve">27287.9297586392</t>
+    <t xml:space="preserve">27268.0846432899</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8286516563134</t>
+    <t xml:space="preserve">24.8264551491546</t>
   </si>
   <si>
-    <t xml:space="preserve">26444.2529898808</t>
+    <t xml:space="preserve">26433.1980706298</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3079783048749</t>
+    <t xml:space="preserve">25.2871120331694</t>
   </si>
   <si>
-    <t xml:space="preserve">25600.5762211225</t>
+    <t xml:space="preserve">25598.3114979697</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7873049534364</t>
+    <t xml:space="preserve">25.7477689171842</t>
   </si>
   <si>
-    <t xml:space="preserve">24926.1204864922</t>
+    <t xml:space="preserve">24931.1920603559</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2650200068262</t>
+    <t xml:space="preserve">26.2335052586429</t>
   </si>
   <si>
-    <t xml:space="preserve">24251.6647518619</t>
+    <t xml:space="preserve">24264.0726227421</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7427350602161</t>
+    <t xml:space="preserve">26.7192416001016</t>
   </si>
   <si>
-    <t xml:space="preserve">23577.2090172317</t>
+    <t xml:space="preserve">23596.9531851283</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2204501136059</t>
+    <t xml:space="preserve">27.2049779415603</t>
   </si>
   <si>
-    <t xml:space="preserve">23515.2699642688</t>
+    <t xml:space="preserve">23534.0243233253</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0576667377089</t>
+    <t xml:space="preserve">28.0646865618077</t>
   </si>
   <si>
-    <t xml:space="preserve">23453.3309113059</t>
+    <t xml:space="preserve">23471.0954615222</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8948833618119</t>
+    <t xml:space="preserve">28.9243951820552</t>
   </si>
   <si>
-    <t xml:space="preserve">23391.391858343</t>
+    <t xml:space="preserve">23408.1665997191</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7320999859148</t>
+    <t xml:space="preserve">29.7841038023026</t>
   </si>
   <si>
-    <t xml:space="preserve">24283.3906890959</t>
+    <t xml:space="preserve">24290.2800119496</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2152887202994</t>
+    <t xml:space="preserve">31.2620551041801</t>
   </si>
   <si>
-    <t xml:space="preserve">25175.3895198488</t>
+    <t xml:space="preserve">25172.3934241801</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6984774546839</t>
+    <t xml:space="preserve">32.7400064060575</t>
   </si>
   <si>
-    <t xml:space="preserve">26067.3883506017</t>
+    <t xml:space="preserve">26054.5068364105</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1816661890684</t>
+    <t xml:space="preserve">34.217957707935</t>
   </si>
   <si>
-    <t xml:space="preserve">28244.3575124532</t>
+    <t xml:space="preserve">28225.9140270887</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8726782159599</t>
+    <t xml:space="preserve">35.9000601903297</t>
   </si>
   <si>
-    <t xml:space="preserve">30421.3266743047</t>
+    <t xml:space="preserve">30397.3212177669</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5636902428514</t>
+    <t xml:space="preserve">37.5821626727245</t>
   </si>
   <si>
-    <t xml:space="preserve">32598.2958361562</t>
+    <t xml:space="preserve">32568.7284084452</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2547022697429</t>
+    <t xml:space="preserve">39.2642651551192</t>
   </si>
   <si>
-    <t xml:space="preserve">34926.8381529243</t>
+    <t xml:space="preserve">34920.9985579674</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3850092849464</t>
+    <t xml:space="preserve">40.4188769577399</t>
   </si>
   <si>
-    <t xml:space="preserve">37255.3804696924</t>
+    <t xml:space="preserve">37273.2687074896</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5153163001499</t>
+    <t xml:space="preserve">41.5734887603606</t>
   </si>
   <si>
-    <t xml:space="preserve">39583.9227864605</t>
+    <t xml:space="preserve">39625.5388570118</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6456233153535</t>
+    <t xml:space="preserve">42.7281005629812</t>
   </si>
   <si>
-    <t xml:space="preserve">41699.8215963146</t>
+    <t xml:space="preserve">41801.0327222036</t>
   </si>
   <si>
-    <t xml:space="preserve">43.3260107086074</t>
+    <t xml:space="preserve">43.4285746975038</t>
   </si>
   <si>
-    <t xml:space="preserve">43815.7204061686</t>
+    <t xml:space="preserve">43976.5265873954</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0063981018613</t>
+    <t xml:space="preserve">44.1290488320263</t>
   </si>
   <si>
-    <t xml:space="preserve">45931.6192160226</t>
+    <t xml:space="preserve">46152.0204525872</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6867854951152</t>
+    <t xml:space="preserve">44.8295229665488</t>
   </si>
   <si>
-    <t xml:space="preserve">47975.6260350731</t>
+    <t xml:space="preserve">48358.7153985657</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4969113884743</t>
+    <t xml:space="preserve">45.7372237000168</t>
   </si>
   <si>
-    <t xml:space="preserve">50019.6328541236</t>
+    <t xml:space="preserve">50565.4103445442</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3070372818334</t>
+    <t xml:space="preserve">46.6449244334849</t>
   </si>
   <si>
-    <t xml:space="preserve">52063.6396731741</t>
+    <t xml:space="preserve">52772.1052905228</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1171631751926</t>
+    <t xml:space="preserve">47.5526251669529</t>
   </si>
   <si>
-    <t xml:space="preserve">53895.0024219569</t>
+    <t xml:space="preserve">55484.9113663333</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1303408979695</t>
+    <t xml:space="preserve">48.862588159554</t>
   </si>
   <si>
-    <t xml:space="preserve">55726.3651707397</t>
+    <t xml:space="preserve">58197.7174421438</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1435186207465</t>
+    <t xml:space="preserve">50.1725511521551</t>
   </si>
   <si>
-    <t xml:space="preserve">57557.7279195225</t>
+    <t xml:space="preserve">60910.5235179543</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1566963435234</t>
+    <t xml:space="preserve">51.4825141447562</t>
   </si>
   <si>
-    <t xml:space="preserve">59695.5047862441</t>
+    <t xml:space="preserve">63737.9740592923</t>
   </si>
   <si>
-    <t xml:space="preserve">52.3077814378196</t>
+    <t xml:space="preserve">52.8101665477419</t>
   </si>
   <si>
-    <t xml:space="preserve">61833.2816529658</t>
+    <t xml:space="preserve">66565.4246006302</t>
   </si>
   <si>
-    <t xml:space="preserve">54.4588665321157</t>
+    <t xml:space="preserve">54.1378189507277</t>
   </si>
   <si>
-    <t xml:space="preserve">63971.0585196874</t>
+    <t xml:space="preserve">69392.8751419682</t>
   </si>
   <si>
-    <t xml:space="preserve">56.6099516264119</t>
+    <t xml:space="preserve">55.4654713537134</t>
   </si>
   <si>
-    <t xml:space="preserve">65898.3233360886</t>
+    <t xml:space="preserve">72301.054118498</t>
   </si>
   <si>
-    <t xml:space="preserve">59.8876313609931</t>
+    <t xml:space="preserve">56.9459479789832</t>
   </si>
   <si>
-    <t xml:space="preserve">67825.5881524897</t>
+    <t xml:space="preserve">75209.2330950278</t>
   </si>
   <si>
-    <t xml:space="preserve">63.1653110955743</t>
+    <t xml:space="preserve">58.4264246042529</t>
   </si>
   <si>
-    <t xml:space="preserve">69752.8529688909</t>
+    <t xml:space="preserve">78117.4120715577</t>
   </si>
   <si>
-    <t xml:space="preserve">66.4429908301556</t>
+    <t xml:space="preserve">59.9069012295226</t>
   </si>
   <si>
-    <t xml:space="preserve">71797.2531874627</t>
+    <t xml:space="preserve">81179.9987479532</t>
   </si>
   <si>
-    <t xml:space="preserve">69.8631200377008</t>
+    <t xml:space="preserve">61.5641098100184</t>
   </si>
   <si>
-    <t xml:space="preserve">73841.6534060345</t>
+    <t xml:space="preserve">84242.5854243487</t>
   </si>
   <si>
-    <t xml:space="preserve">73.2832492452461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75886.0536246063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.7033784527913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77958.4078223623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2669446280965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80030.7620201183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8305108034016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82103.1162178743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.3940769787068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84157.010449528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.0613851904835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86210.9046811817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.7286934022601</t>
+    <t xml:space="preserve">63.2213183905142</t>
   </si>
 </sst>
 </file>
@@ -1790,13 +1754,13 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>3689084</v>
+        <v>3520661</v>
       </c>
       <c r="D2" t="n">
-        <v>12198</v>
+        <v>11789</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00330651186039678</v>
+        <v>0.00334851892868981</v>
       </c>
     </row>
     <row r="3">
@@ -1807,13 +1771,13 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>2464011</v>
+        <v>2248557</v>
       </c>
       <c r="D3" t="n">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000285713010209776</v>
+        <v>0.000306863468437758</v>
       </c>
     </row>
     <row r="4">
@@ -1892,13 +1856,13 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>2553</v>
+        <v>2509</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0.000391696043869957</v>
+        <v>0.000398565165404544</v>
       </c>
     </row>
     <row r="9">
@@ -1909,13 +1873,13 @@
         <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>864962</v>
+        <v>834325</v>
       </c>
       <c r="D9" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0000820845308811254</v>
+        <v>0.0000815030114164145</v>
       </c>
     </row>
     <row r="10">
@@ -1926,13 +1890,13 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>202462</v>
+        <v>200363</v>
       </c>
       <c r="D10" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E10" t="n">
-        <v>0.000933508510238958</v>
+        <v>0.000938296990961405</v>
       </c>
     </row>
     <row r="11">
@@ -1943,13 +1907,13 @@
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>123921</v>
+        <v>120855</v>
       </c>
       <c r="D11" t="n">
         <v>93</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000750478127193938</v>
+        <v>0.0007695171900211</v>
       </c>
     </row>
     <row r="12">
@@ -1960,13 +1924,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>88491</v>
+        <v>88238</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0000113005842402052</v>
+        <v>0.0000113329857884358</v>
       </c>
     </row>
     <row r="13">
@@ -1977,13 +1941,13 @@
         <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>57295</v>
+        <v>55753</v>
       </c>
       <c r="D13" t="n">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0135613927916921</v>
+        <v>0.013649489713558</v>
       </c>
     </row>
     <row r="14">
@@ -1994,13 +1958,13 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>4508</v>
+        <v>4003</v>
       </c>
       <c r="D14" t="n">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0532386867790594</v>
+        <v>0.0534599050711966</v>
       </c>
     </row>
     <row r="15">
@@ -2028,7 +1992,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>143173</v>
+        <v>135328</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -2045,13 +2009,13 @@
         <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>114459</v>
+        <v>105060</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0000873675289841777</v>
+        <v>0.000418808300019037</v>
       </c>
     </row>
     <row r="18">
@@ -2062,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="C18" t="n">
-        <v>113739</v>
+        <v>101693</v>
       </c>
       <c r="D18" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>0.000386850596541204</v>
+        <v>0.0000786681482501254</v>
       </c>
     </row>
     <row r="19">
@@ -2079,7 +2043,7 @@
         <v>25</v>
       </c>
       <c r="C19" t="n">
-        <v>52431</v>
+        <v>48037</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -2096,7 +2060,7 @@
         <v>26</v>
       </c>
       <c r="C20" t="n">
-        <v>33025</v>
+        <v>30608</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -2113,7 +2077,7 @@
         <v>27</v>
       </c>
       <c r="C21" t="n">
-        <v>15171</v>
+        <v>14034</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2130,13 +2094,13 @@
         <v>28</v>
       </c>
       <c r="C22" t="n">
-        <v>13657</v>
+        <v>12208</v>
       </c>
       <c r="D22" t="n">
         <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>0.000366112616240756</v>
+        <v>0.00040956749672346</v>
       </c>
     </row>
     <row r="23">
@@ -2147,13 +2111,13 @@
         <v>29</v>
       </c>
       <c r="C23" t="n">
-        <v>1481</v>
+        <v>1427</v>
       </c>
       <c r="D23" t="n">
         <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00202565833896016</v>
+        <v>0.00210231254379818</v>
       </c>
     </row>
     <row r="24">
@@ -2164,13 +2128,13 @@
         <v>31</v>
       </c>
       <c r="C24" t="n">
-        <v>906155</v>
+        <v>892301</v>
       </c>
       <c r="D24" t="n">
         <v>18</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0000198641512765476</v>
+        <v>0.0000201725650873416</v>
       </c>
     </row>
     <row r="25">
@@ -2181,7 +2145,7 @@
         <v>32</v>
       </c>
       <c r="C25" t="n">
-        <v>102334</v>
+        <v>101978</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -2198,13 +2162,13 @@
         <v>33</v>
       </c>
       <c r="C26" t="n">
-        <v>48788</v>
+        <v>47612</v>
       </c>
       <c r="D26" t="n">
         <v>11</v>
       </c>
       <c r="E26" t="n">
-        <v>0.000225465278347135</v>
+        <v>0.000231034193060573</v>
       </c>
     </row>
     <row r="27">
@@ -2215,7 +2179,7 @@
         <v>34</v>
       </c>
       <c r="C27" t="n">
-        <v>5421</v>
+        <v>5391</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -2232,13 +2196,13 @@
         <v>35</v>
       </c>
       <c r="C28" t="n">
-        <v>2075</v>
+        <v>1340</v>
       </c>
       <c r="D28" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="E28" t="n">
-        <v>0.00674698795180723</v>
+        <v>0.0529850746268657</v>
       </c>
     </row>
     <row r="29">
@@ -2249,13 +2213,13 @@
         <v>36</v>
       </c>
       <c r="C29" t="n">
-        <v>1367</v>
+        <v>1042</v>
       </c>
       <c r="D29" t="n">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0541331382589612</v>
+        <v>0.0124760076775432</v>
       </c>
     </row>
     <row r="30">
@@ -2266,13 +2230,13 @@
         <v>38</v>
       </c>
       <c r="C30" t="n">
-        <v>796006</v>
+        <v>772629</v>
       </c>
       <c r="D30" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0000402007020047588</v>
+        <v>0.0000401227497285243</v>
       </c>
     </row>
     <row r="31">
@@ -2283,13 +2247,13 @@
         <v>39</v>
       </c>
       <c r="C31" t="n">
-        <v>48648</v>
+        <v>47106</v>
       </c>
       <c r="D31" t="n">
-        <v>809</v>
+        <v>769</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0166296661733268</v>
+        <v>0.0163248843034858</v>
       </c>
     </row>
     <row r="32">
@@ -2300,13 +2264,13 @@
         <v>40</v>
       </c>
       <c r="C32" t="n">
-        <v>42034</v>
+        <v>41065</v>
       </c>
       <c r="D32" t="n">
         <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0000713707950706571</v>
+        <v>0.0000730549129428954</v>
       </c>
     </row>
     <row r="33">
@@ -2317,13 +2281,13 @@
         <v>41</v>
       </c>
       <c r="C33" t="n">
-        <v>40679</v>
+        <v>40547</v>
       </c>
       <c r="D33" t="n">
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0000491654170456501</v>
+        <v>0.0000493254741411202</v>
       </c>
     </row>
     <row r="34">
@@ -2334,13 +2298,13 @@
         <v>42</v>
       </c>
       <c r="C34" t="n">
-        <v>36250</v>
+        <v>35403</v>
       </c>
       <c r="D34" t="n">
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0000275862068965517</v>
+        <v>0.000028246193825382</v>
       </c>
     </row>
     <row r="35">
@@ -2351,13 +2315,13 @@
         <v>43</v>
       </c>
       <c r="C35" t="n">
-        <v>8609</v>
+        <v>8302</v>
       </c>
       <c r="D35" t="n">
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>0.000116157509582995</v>
+        <v>0.00012045290291496</v>
       </c>
     </row>
     <row r="36">
@@ -2368,7 +2332,7 @@
         <v>44</v>
       </c>
       <c r="C36" t="n">
-        <v>8114</v>
+        <v>7067</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -2385,13 +2349,13 @@
         <v>45</v>
       </c>
       <c r="C37" t="n">
-        <v>4789</v>
+        <v>4698</v>
       </c>
       <c r="D37" t="n">
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>0.000208811860513677</v>
+        <v>0.000212856534695615</v>
       </c>
     </row>
     <row r="38">
@@ -2402,13 +2366,13 @@
         <v>46</v>
       </c>
       <c r="C38" t="n">
-        <v>3679</v>
+        <v>3674</v>
       </c>
       <c r="D38" t="n">
         <v>35</v>
       </c>
       <c r="E38" t="n">
-        <v>0.00951345474313672</v>
+        <v>0.00952640174197061</v>
       </c>
     </row>
   </sheetData>
@@ -5907,108 +5871,6 @@
         <v>457</v>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B206" t="n">
-        <v>112337</v>
-      </c>
-      <c r="C206" t="n">
-        <v>85</v>
-      </c>
-      <c r="D206" t="s">
-        <v>458</v>
-      </c>
-      <c r="E206" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B207" t="n">
-        <v>91699</v>
-      </c>
-      <c r="C207" t="n">
-        <v>88</v>
-      </c>
-      <c r="D207" t="s">
-        <v>460</v>
-      </c>
-      <c r="E207" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B208" t="n">
-        <v>82768</v>
-      </c>
-      <c r="C208" t="n">
-        <v>77</v>
-      </c>
-      <c r="D208" t="s">
-        <v>462</v>
-      </c>
-      <c r="E208" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B209" t="n">
-        <v>63945</v>
-      </c>
-      <c r="C209" t="n">
-        <v>108</v>
-      </c>
-      <c r="D209" t="s">
-        <v>464</v>
-      </c>
-      <c r="E209" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B210" t="n">
-        <v>62255</v>
-      </c>
-      <c r="C210" t="n">
-        <v>107</v>
-      </c>
-      <c r="D210" t="s">
-        <v>466</v>
-      </c>
-      <c r="E210" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B211" t="n">
-        <v>92553</v>
-      </c>
-      <c r="C211" t="n">
-        <v>51</v>
-      </c>
-      <c r="D211" t="s">
-        <v>468</v>
-      </c>
-      <c r="E211" t="s">
-        <v>469</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -6045,13 +5907,13 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>3689084</v>
+        <v>3520661</v>
       </c>
       <c r="D2" t="n">
-        <v>12198</v>
+        <v>11789</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00330651186039678</v>
+        <v>0.00334851892868981</v>
       </c>
     </row>
     <row r="3">
@@ -6062,13 +5924,13 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>2464011</v>
+        <v>2248557</v>
       </c>
       <c r="D3" t="n">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000285713010209776</v>
+        <v>0.000306863468437758</v>
       </c>
     </row>
     <row r="4">
@@ -6147,13 +6009,13 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>2553</v>
+        <v>2509</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0.000391696043869957</v>
+        <v>0.000398565165404544</v>
       </c>
     </row>
     <row r="9">
@@ -6164,13 +6026,13 @@
         <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>864962</v>
+        <v>834325</v>
       </c>
       <c r="D9" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0000820845308811254</v>
+        <v>0.0000815030114164145</v>
       </c>
     </row>
     <row r="10">
@@ -6181,13 +6043,13 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>202462</v>
+        <v>200363</v>
       </c>
       <c r="D10" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E10" t="n">
-        <v>0.000933508510238958</v>
+        <v>0.000938296990961405</v>
       </c>
     </row>
     <row r="11">
@@ -6198,13 +6060,13 @@
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>123921</v>
+        <v>120855</v>
       </c>
       <c r="D11" t="n">
         <v>93</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000750478127193938</v>
+        <v>0.0007695171900211</v>
       </c>
     </row>
     <row r="12">
@@ -6215,13 +6077,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>88491</v>
+        <v>88238</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0000113005842402052</v>
+        <v>0.0000113329857884358</v>
       </c>
     </row>
     <row r="13">
@@ -6232,13 +6094,13 @@
         <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>57295</v>
+        <v>55753</v>
       </c>
       <c r="D13" t="n">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0135613927916921</v>
+        <v>0.013649489713558</v>
       </c>
     </row>
     <row r="14">
@@ -6249,13 +6111,13 @@
         <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>4508</v>
+        <v>4003</v>
       </c>
       <c r="D14" t="n">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0532386867790594</v>
+        <v>0.0534599050711966</v>
       </c>
     </row>
     <row r="15">
@@ -6283,7 +6145,7 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>143173</v>
+        <v>135328</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -6300,13 +6162,13 @@
         <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>114459</v>
+        <v>105060</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0000873675289841777</v>
+        <v>0.000418808300019037</v>
       </c>
     </row>
     <row r="18">
@@ -6317,13 +6179,13 @@
         <v>24</v>
       </c>
       <c r="C18" t="n">
-        <v>113739</v>
+        <v>101693</v>
       </c>
       <c r="D18" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>0.000386850596541204</v>
+        <v>0.0000786681482501254</v>
       </c>
     </row>
     <row r="19">
@@ -6334,7 +6196,7 @@
         <v>25</v>
       </c>
       <c r="C19" t="n">
-        <v>52431</v>
+        <v>48037</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -6351,7 +6213,7 @@
         <v>26</v>
       </c>
       <c r="C20" t="n">
-        <v>33025</v>
+        <v>30608</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -6368,7 +6230,7 @@
         <v>27</v>
       </c>
       <c r="C21" t="n">
-        <v>15171</v>
+        <v>14034</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -6385,13 +6247,13 @@
         <v>28</v>
       </c>
       <c r="C22" t="n">
-        <v>13657</v>
+        <v>12208</v>
       </c>
       <c r="D22" t="n">
         <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>0.000366112616240756</v>
+        <v>0.00040956749672346</v>
       </c>
     </row>
     <row r="23">
@@ -6402,13 +6264,13 @@
         <v>29</v>
       </c>
       <c r="C23" t="n">
-        <v>1481</v>
+        <v>1427</v>
       </c>
       <c r="D23" t="n">
         <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00202565833896016</v>
+        <v>0.00210231254379818</v>
       </c>
     </row>
     <row r="24">
@@ -6419,13 +6281,13 @@
         <v>31</v>
       </c>
       <c r="C24" t="n">
-        <v>906155</v>
+        <v>892301</v>
       </c>
       <c r="D24" t="n">
         <v>18</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0000198641512765476</v>
+        <v>0.0000201725650873416</v>
       </c>
     </row>
     <row r="25">
@@ -6436,7 +6298,7 @@
         <v>32</v>
       </c>
       <c r="C25" t="n">
-        <v>102334</v>
+        <v>101978</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -6453,13 +6315,13 @@
         <v>33</v>
       </c>
       <c r="C26" t="n">
-        <v>48788</v>
+        <v>47612</v>
       </c>
       <c r="D26" t="n">
         <v>11</v>
       </c>
       <c r="E26" t="n">
-        <v>0.000225465278347135</v>
+        <v>0.000231034193060573</v>
       </c>
     </row>
     <row r="27">
@@ -6470,7 +6332,7 @@
         <v>34</v>
       </c>
       <c r="C27" t="n">
-        <v>5421</v>
+        <v>5391</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -6487,13 +6349,13 @@
         <v>35</v>
       </c>
       <c r="C28" t="n">
-        <v>2075</v>
+        <v>1340</v>
       </c>
       <c r="D28" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="E28" t="n">
-        <v>0.00674698795180723</v>
+        <v>0.0529850746268657</v>
       </c>
     </row>
     <row r="29">
@@ -6504,13 +6366,13 @@
         <v>36</v>
       </c>
       <c r="C29" t="n">
-        <v>1367</v>
+        <v>1042</v>
       </c>
       <c r="D29" t="n">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0541331382589612</v>
+        <v>0.0124760076775432</v>
       </c>
     </row>
     <row r="30">
@@ -6521,13 +6383,13 @@
         <v>38</v>
       </c>
       <c r="C30" t="n">
-        <v>796006</v>
+        <v>772629</v>
       </c>
       <c r="D30" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0000402007020047588</v>
+        <v>0.0000401227497285243</v>
       </c>
     </row>
     <row r="31">
@@ -6538,13 +6400,13 @@
         <v>39</v>
       </c>
       <c r="C31" t="n">
-        <v>48648</v>
+        <v>47106</v>
       </c>
       <c r="D31" t="n">
-        <v>809</v>
+        <v>769</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0166296661733268</v>
+        <v>0.0163248843034858</v>
       </c>
     </row>
     <row r="32">
@@ -6555,13 +6417,13 @@
         <v>40</v>
       </c>
       <c r="C32" t="n">
-        <v>42034</v>
+        <v>41065</v>
       </c>
       <c r="D32" t="n">
         <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0000713707950706571</v>
+        <v>0.0000730549129428954</v>
       </c>
     </row>
     <row r="33">
@@ -6572,13 +6434,13 @@
         <v>41</v>
       </c>
       <c r="C33" t="n">
-        <v>40679</v>
+        <v>40547</v>
       </c>
       <c r="D33" t="n">
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0000491654170456501</v>
+        <v>0.0000493254741411202</v>
       </c>
     </row>
     <row r="34">
@@ -6589,13 +6451,13 @@
         <v>42</v>
       </c>
       <c r="C34" t="n">
-        <v>36250</v>
+        <v>35403</v>
       </c>
       <c r="D34" t="n">
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0000275862068965517</v>
+        <v>0.000028246193825382</v>
       </c>
     </row>
     <row r="35">
@@ -6606,13 +6468,13 @@
         <v>43</v>
       </c>
       <c r="C35" t="n">
-        <v>8609</v>
+        <v>8302</v>
       </c>
       <c r="D35" t="n">
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>0.000116157509582995</v>
+        <v>0.00012045290291496</v>
       </c>
     </row>
     <row r="36">
@@ -6623,7 +6485,7 @@
         <v>44</v>
       </c>
       <c r="C36" t="n">
-        <v>8114</v>
+        <v>7067</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -6640,13 +6502,13 @@
         <v>45</v>
       </c>
       <c r="C37" t="n">
-        <v>4789</v>
+        <v>4698</v>
       </c>
       <c r="D37" t="n">
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>0.000208811860513677</v>
+        <v>0.000212856534695615</v>
       </c>
     </row>
     <row r="38">
@@ -6657,13 +6519,13 @@
         <v>46</v>
       </c>
       <c r="C38" t="n">
-        <v>3679</v>
+        <v>3674</v>
       </c>
       <c r="D38" t="n">
         <v>35</v>
       </c>
       <c r="E38" t="n">
-        <v>0.00951345474313672</v>
+        <v>0.00952640174197061</v>
       </c>
     </row>
   </sheetData>
@@ -10162,108 +10024,6 @@
         <v>457</v>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B206" t="n">
-        <v>112337</v>
-      </c>
-      <c r="C206" t="n">
-        <v>85</v>
-      </c>
-      <c r="D206" t="s">
-        <v>458</v>
-      </c>
-      <c r="E206" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B207" t="n">
-        <v>91699</v>
-      </c>
-      <c r="C207" t="n">
-        <v>88</v>
-      </c>
-      <c r="D207" t="s">
-        <v>460</v>
-      </c>
-      <c r="E207" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B208" t="n">
-        <v>82768</v>
-      </c>
-      <c r="C208" t="n">
-        <v>77</v>
-      </c>
-      <c r="D208" t="s">
-        <v>462</v>
-      </c>
-      <c r="E208" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B209" t="n">
-        <v>63945</v>
-      </c>
-      <c r="C209" t="n">
-        <v>108</v>
-      </c>
-      <c r="D209" t="s">
-        <v>464</v>
-      </c>
-      <c r="E209" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B210" t="n">
-        <v>62255</v>
-      </c>
-      <c r="C210" t="n">
-        <v>107</v>
-      </c>
-      <c r="D210" t="s">
-        <v>466</v>
-      </c>
-      <c r="E210" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B211" t="n">
-        <v>92553</v>
-      </c>
-      <c r="C211" t="n">
-        <v>51</v>
-      </c>
-      <c r="D211" t="s">
-        <v>468</v>
-      </c>
-      <c r="E211" t="s">
-        <v>469</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -21506,336 +21266,6 @@
         <v>4781</v>
       </c>
     </row>
-    <row r="1022">
-      <c r="A1022" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B1022" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1022" t="n">
-        <v>85572</v>
-      </c>
-    </row>
-    <row r="1023">
-      <c r="A1023" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B1023" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1023" t="n">
-        <v>10301</v>
-      </c>
-    </row>
-    <row r="1024">
-      <c r="A1024" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B1024" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1024" t="n">
-        <v>6903</v>
-      </c>
-    </row>
-    <row r="1025">
-      <c r="A1025" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B1025" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1025" t="n">
-        <v>2985</v>
-      </c>
-    </row>
-    <row r="1026">
-      <c r="A1026" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B1026" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1026" t="n">
-        <v>6576</v>
-      </c>
-    </row>
-    <row r="1027">
-      <c r="A1027" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B1027" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1027" t="n">
-        <v>69374</v>
-      </c>
-    </row>
-    <row r="1028">
-      <c r="A1028" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B1028" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1028" t="n">
-        <v>6073</v>
-      </c>
-    </row>
-    <row r="1029">
-      <c r="A1029" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B1029" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1029" t="n">
-        <v>6352</v>
-      </c>
-    </row>
-    <row r="1030">
-      <c r="A1030" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B1030" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1030" t="n">
-        <v>3246</v>
-      </c>
-    </row>
-    <row r="1031">
-      <c r="A1031" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B1031" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1031" t="n">
-        <v>6654</v>
-      </c>
-    </row>
-    <row r="1032">
-      <c r="A1032" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B1032" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1032" t="n">
-        <v>62365</v>
-      </c>
-    </row>
-    <row r="1033">
-      <c r="A1033" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B1033" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1033" t="n">
-        <v>4938</v>
-      </c>
-    </row>
-    <row r="1034">
-      <c r="A1034" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B1034" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1034" t="n">
-        <v>6650</v>
-      </c>
-    </row>
-    <row r="1035">
-      <c r="A1035" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B1035" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1035" t="n">
-        <v>3299</v>
-      </c>
-    </row>
-    <row r="1036">
-      <c r="A1036" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B1036" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1036" t="n">
-        <v>5516</v>
-      </c>
-    </row>
-    <row r="1037">
-      <c r="A1037" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B1037" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1037" t="n">
-        <v>48486</v>
-      </c>
-    </row>
-    <row r="1038">
-      <c r="A1038" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B1038" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1038" t="n">
-        <v>4203</v>
-      </c>
-    </row>
-    <row r="1039">
-      <c r="A1039" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B1039" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1039" t="n">
-        <v>6235</v>
-      </c>
-    </row>
-    <row r="1040">
-      <c r="A1040" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B1040" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1040" t="n">
-        <v>2453</v>
-      </c>
-    </row>
-    <row r="1041">
-      <c r="A1041" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B1041" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1041" t="n">
-        <v>2568</v>
-      </c>
-    </row>
-    <row r="1042">
-      <c r="A1042" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B1042" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1042" t="n">
-        <v>46016</v>
-      </c>
-    </row>
-    <row r="1043">
-      <c r="A1043" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B1043" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1043" t="n">
-        <v>4577</v>
-      </c>
-    </row>
-    <row r="1044">
-      <c r="A1044" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B1044" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1044" t="n">
-        <v>6961</v>
-      </c>
-    </row>
-    <row r="1045">
-      <c r="A1045" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B1045" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1045" t="n">
-        <v>2267</v>
-      </c>
-    </row>
-    <row r="1046">
-      <c r="A1046" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B1046" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1046" t="n">
-        <v>2434</v>
-      </c>
-    </row>
-    <row r="1047">
-      <c r="A1047" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B1047" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1047" t="n">
-        <v>72108</v>
-      </c>
-    </row>
-    <row r="1048">
-      <c r="A1048" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B1048" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1048" t="n">
-        <v>8010</v>
-      </c>
-    </row>
-    <row r="1049">
-      <c r="A1049" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B1049" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1049" t="n">
-        <v>5640</v>
-      </c>
-    </row>
-    <row r="1050">
-      <c r="A1050" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B1050" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1050" t="n">
-        <v>2226</v>
-      </c>
-    </row>
-    <row r="1051">
-      <c r="A1051" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B1051" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1051" t="n">
-        <v>4569</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -33078,336 +32508,6 @@
         <v>0.0558847938656474</v>
       </c>
     </row>
-    <row r="1022">
-      <c r="A1022" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B1022" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1022" t="n">
-        <v>0.761743681956969</v>
-      </c>
-    </row>
-    <row r="1023">
-      <c r="A1023" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B1023" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1023" t="n">
-        <v>0.0916973036488423</v>
-      </c>
-    </row>
-    <row r="1024">
-      <c r="A1024" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B1024" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1024" t="n">
-        <v>0.0614490328208872</v>
-      </c>
-    </row>
-    <row r="1025">
-      <c r="A1025" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B1025" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1025" t="n">
-        <v>0.0265718329668765</v>
-      </c>
-    </row>
-    <row r="1026">
-      <c r="A1026" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B1026" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1026" t="n">
-        <v>0.0585381486064253</v>
-      </c>
-    </row>
-    <row r="1027">
-      <c r="A1027" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B1027" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1027" t="n">
-        <v>0.756540420288117</v>
-      </c>
-    </row>
-    <row r="1028">
-      <c r="A1028" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B1028" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1028" t="n">
-        <v>0.0662275488282315</v>
-      </c>
-    </row>
-    <row r="1029">
-      <c r="A1029" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B1029" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1029" t="n">
-        <v>0.0692701119968593</v>
-      </c>
-    </row>
-    <row r="1030">
-      <c r="A1030" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B1030" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1030" t="n">
-        <v>0.0353984231016696</v>
-      </c>
-    </row>
-    <row r="1031">
-      <c r="A1031" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B1031" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1031" t="n">
-        <v>0.0725634957851231</v>
-      </c>
-    </row>
-    <row r="1032">
-      <c r="A1032" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B1032" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1032" t="n">
-        <v>0.753491687608738</v>
-      </c>
-    </row>
-    <row r="1033">
-      <c r="A1033" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B1033" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1033" t="n">
-        <v>0.0596607384496424</v>
-      </c>
-    </row>
-    <row r="1034">
-      <c r="A1034" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B1034" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1034" t="n">
-        <v>0.0803450608930988</v>
-      </c>
-    </row>
-    <row r="1035">
-      <c r="A1035" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B1035" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1035" t="n">
-        <v>0.0398583993814034</v>
-      </c>
-    </row>
-    <row r="1036">
-      <c r="A1036" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B1036" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1036" t="n">
-        <v>0.0666441136671177</v>
-      </c>
-    </row>
-    <row r="1037">
-      <c r="A1037" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B1037" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1037" t="n">
-        <v>0.758245367112362</v>
-      </c>
-    </row>
-    <row r="1038">
-      <c r="A1038" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B1038" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1038" t="n">
-        <v>0.0657283603096411</v>
-      </c>
-    </row>
-    <row r="1039">
-      <c r="A1039" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B1039" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1039" t="n">
-        <v>0.0975056689342404</v>
-      </c>
-    </row>
-    <row r="1040">
-      <c r="A1040" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B1040" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1040" t="n">
-        <v>0.038361091563062</v>
-      </c>
-    </row>
-    <row r="1041">
-      <c r="A1041" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B1041" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1041" t="n">
-        <v>0.0401595120806943</v>
-      </c>
-    </row>
-    <row r="1042">
-      <c r="A1042" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B1042" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1042" t="n">
-        <v>0.73915348164806</v>
-      </c>
-    </row>
-    <row r="1043">
-      <c r="A1043" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B1043" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1043" t="n">
-        <v>0.0735201991807887</v>
-      </c>
-    </row>
-    <row r="1044">
-      <c r="A1044" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B1044" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1044" t="n">
-        <v>0.111814312103446</v>
-      </c>
-    </row>
-    <row r="1045">
-      <c r="A1045" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B1045" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1045" t="n">
-        <v>0.0364147458035499</v>
-      </c>
-    </row>
-    <row r="1046">
-      <c r="A1046" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B1046" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1046" t="n">
-        <v>0.0390972612641555</v>
-      </c>
-    </row>
-    <row r="1047">
-      <c r="A1047" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B1047" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1047" t="n">
-        <v>0.779099542964572</v>
-      </c>
-    </row>
-    <row r="1048">
-      <c r="A1048" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B1048" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1048" t="n">
-        <v>0.0865450066448413</v>
-      </c>
-    </row>
-    <row r="1049">
-      <c r="A1049" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B1049" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1049" t="n">
-        <v>0.0609380571132216</v>
-      </c>
-    </row>
-    <row r="1050">
-      <c r="A1050" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B1050" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1050" t="n">
-        <v>0.0240510842436226</v>
-      </c>
-    </row>
-    <row r="1051">
-      <c r="A1051" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B1051" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1051" t="n">
-        <v>0.0493663090337428</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -44650,336 +43750,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1022">
-      <c r="A1022" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B1022" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1022" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="1023">
-      <c r="A1023" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B1023" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1023" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="1024">
-      <c r="A1024" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B1024" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1024" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1025">
-      <c r="A1025" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B1025" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1025" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1026">
-      <c r="A1026" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B1026" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1026" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="1027">
-      <c r="A1027" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B1027" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1027" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="1028">
-      <c r="A1028" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B1028" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1028" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="1029">
-      <c r="A1029" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B1029" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1029" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1030">
-      <c r="A1030" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B1030" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1030" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1031">
-      <c r="A1031" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B1031" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1031" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="1032">
-      <c r="A1032" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B1032" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1032" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="1033">
-      <c r="A1033" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B1033" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1033" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1034">
-      <c r="A1034" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B1034" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1034" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1035">
-      <c r="A1035" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B1035" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1035" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1036">
-      <c r="A1036" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B1036" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1036" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="1037">
-      <c r="A1037" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B1037" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1037" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="1038">
-      <c r="A1038" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B1038" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1038" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="1039">
-      <c r="A1039" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B1039" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1039" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1040">
-      <c r="A1040" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B1040" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1040" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1041">
-      <c r="A1041" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B1041" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1041" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="1042">
-      <c r="A1042" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B1042" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1042" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="1043">
-      <c r="A1043" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B1043" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1043" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="1044">
-      <c r="A1044" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B1044" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1044" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1045">
-      <c r="A1045" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B1045" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1045" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1046">
-      <c r="A1046" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B1046" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1046" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1047">
-      <c r="A1047" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B1047" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1047" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="1048">
-      <c r="A1048" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B1048" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1048" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="1049">
-      <c r="A1049" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B1049" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1049" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1050">
-      <c r="A1050" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B1050" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1050" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1051">
-      <c r="A1051" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B1051" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1051" t="n">
-        <v>6</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -56222,336 +54992,6 @@
         <v>0.0625</v>
       </c>
     </row>
-    <row r="1022">
-      <c r="A1022" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B1022" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1022" t="n">
-        <v>0.835294117647059</v>
-      </c>
-    </row>
-    <row r="1023">
-      <c r="A1023" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B1023" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1023" t="n">
-        <v>0.105882352941176</v>
-      </c>
-    </row>
-    <row r="1024">
-      <c r="A1024" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B1024" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1024" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1025">
-      <c r="A1025" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B1025" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1025" t="n">
-        <v>0.0117647058823529</v>
-      </c>
-    </row>
-    <row r="1026">
-      <c r="A1026" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B1026" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1026" t="n">
-        <v>0.0470588235294118</v>
-      </c>
-    </row>
-    <row r="1027">
-      <c r="A1027" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B1027" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1027" t="n">
-        <v>0.784090909090909</v>
-      </c>
-    </row>
-    <row r="1028">
-      <c r="A1028" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B1028" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1028" t="n">
-        <v>0.102272727272727</v>
-      </c>
-    </row>
-    <row r="1029">
-      <c r="A1029" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B1029" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1029" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1030">
-      <c r="A1030" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B1030" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1030" t="n">
-        <v>0.0113636363636364</v>
-      </c>
-    </row>
-    <row r="1031">
-      <c r="A1031" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B1031" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1031" t="n">
-        <v>0.102272727272727</v>
-      </c>
-    </row>
-    <row r="1032">
-      <c r="A1032" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B1032" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1032" t="n">
-        <v>0.922077922077922</v>
-      </c>
-    </row>
-    <row r="1033">
-      <c r="A1033" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B1033" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1033" t="n">
-        <v>0.012987012987013</v>
-      </c>
-    </row>
-    <row r="1034">
-      <c r="A1034" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B1034" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1034" t="n">
-        <v>0.012987012987013</v>
-      </c>
-    </row>
-    <row r="1035">
-      <c r="A1035" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B1035" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1035" t="n">
-        <v>0.012987012987013</v>
-      </c>
-    </row>
-    <row r="1036">
-      <c r="A1036" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B1036" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1036" t="n">
-        <v>0.038961038961039</v>
-      </c>
-    </row>
-    <row r="1037">
-      <c r="A1037" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B1037" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1037" t="n">
-        <v>0.759259259259259</v>
-      </c>
-    </row>
-    <row r="1038">
-      <c r="A1038" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B1038" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1038" t="n">
-        <v>0.157407407407407</v>
-      </c>
-    </row>
-    <row r="1039">
-      <c r="A1039" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B1039" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1039" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1040">
-      <c r="A1040" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B1040" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1040" t="n">
-        <v>0.00925925925925926</v>
-      </c>
-    </row>
-    <row r="1041">
-      <c r="A1041" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B1041" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1041" t="n">
-        <v>0.0740740740740741</v>
-      </c>
-    </row>
-    <row r="1042">
-      <c r="A1042" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B1042" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1042" t="n">
-        <v>0.841121495327103</v>
-      </c>
-    </row>
-    <row r="1043">
-      <c r="A1043" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B1043" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1043" t="n">
-        <v>0.0560747663551402</v>
-      </c>
-    </row>
-    <row r="1044">
-      <c r="A1044" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B1044" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1044" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1045">
-      <c r="A1045" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B1045" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1045" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1046">
-      <c r="A1046" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B1046" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1046" t="n">
-        <v>0.102803738317757</v>
-      </c>
-    </row>
-    <row r="1047">
-      <c r="A1047" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B1047" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1047" t="n">
-        <v>0.784313725490196</v>
-      </c>
-    </row>
-    <row r="1048">
-      <c r="A1048" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B1048" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1048" t="n">
-        <v>0.0784313725490196</v>
-      </c>
-    </row>
-    <row r="1049">
-      <c r="A1049" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B1049" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1049" t="n">
-        <v>0.0196078431372549</v>
-      </c>
-    </row>
-    <row r="1050">
-      <c r="A1050" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B1050" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1050" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1051">
-      <c r="A1051" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B1051" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1051" t="n">
-        <v>0.117647058823529</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
